--- a/力扣学习计划/刷题进度表.xlsx
+++ b/力扣学习计划/刷题进度表.xlsx
@@ -872,12 +872,14 @@
         </is>
       </c>
       <c r="G4" s="26" t="n"/>
-      <c r="H4" s="29" t="n"/>
+      <c r="H4" s="29" t="n">
+        <v>46305</v>
+      </c>
       <c r="I4" s="26" t="n"/>
       <c r="J4" s="29" t="n"/>
       <c r="K4" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L4" s="27" t="n"/>
@@ -1322,12 +1324,14 @@
         </is>
       </c>
       <c r="G14" s="26" t="n"/>
-      <c r="H14" s="29" t="n"/>
+      <c r="H14" s="29" t="n">
+        <v>46305</v>
+      </c>
       <c r="I14" s="26" t="n"/>
       <c r="J14" s="29" t="n"/>
       <c r="K14" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L14" s="27" t="n"/>
@@ -1360,12 +1364,14 @@
         </is>
       </c>
       <c r="G15" s="26" t="n"/>
-      <c r="H15" s="29" t="n"/>
+      <c r="H15" s="29" t="n">
+        <v>46306</v>
+      </c>
       <c r="I15" s="26" t="n"/>
       <c r="J15" s="29" t="n"/>
       <c r="K15" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L15" s="27" t="n"/>
@@ -1442,12 +1448,14 @@
         </is>
       </c>
       <c r="G17" s="26" t="n"/>
-      <c r="H17" s="29" t="n"/>
+      <c r="H17" s="29" t="n">
+        <v>46306</v>
+      </c>
       <c r="I17" s="26" t="n"/>
       <c r="J17" s="29" t="n"/>
       <c r="K17" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L17" s="27" t="n"/>
@@ -1480,12 +1488,14 @@
         </is>
       </c>
       <c r="G18" s="26" t="n"/>
-      <c r="H18" s="29" t="n"/>
+      <c r="H18" s="29" t="n">
+        <v>46306</v>
+      </c>
       <c r="I18" s="26" t="n"/>
       <c r="J18" s="29" t="n"/>
       <c r="K18" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L18" s="27" t="n"/>
@@ -1518,12 +1528,14 @@
         </is>
       </c>
       <c r="G19" s="26" t="n"/>
-      <c r="H19" s="29" t="n"/>
+      <c r="H19" s="29" t="n">
+        <v>46307</v>
+      </c>
       <c r="I19" s="26" t="n"/>
       <c r="J19" s="29" t="n"/>
       <c r="K19" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L19" s="27" t="n"/>
@@ -1556,12 +1568,14 @@
         </is>
       </c>
       <c r="G20" s="26" t="n"/>
-      <c r="H20" s="29" t="n"/>
+      <c r="H20" s="29" t="n">
+        <v>46308</v>
+      </c>
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="29" t="n"/>
       <c r="K20" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L20" s="27" t="n"/>
@@ -1594,12 +1608,14 @@
         </is>
       </c>
       <c r="G21" s="26" t="n"/>
-      <c r="H21" s="29" t="n"/>
+      <c r="H21" s="29" t="n">
+        <v>46301</v>
+      </c>
       <c r="I21" s="26" t="n"/>
       <c r="J21" s="29" t="n"/>
       <c r="K21" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L21" s="27" t="n"/>

--- a/力扣学习计划/刷题进度表.xlsx
+++ b/力扣学习计划/刷题进度表.xlsx
@@ -1648,12 +1648,14 @@
         </is>
       </c>
       <c r="G22" s="26" t="n"/>
-      <c r="H22" s="29" t="n"/>
+      <c r="H22" s="29" t="n">
+        <v>46309</v>
+      </c>
       <c r="I22" s="26" t="n"/>
       <c r="J22" s="29" t="n"/>
       <c r="K22" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L22" s="27" t="n"/>
@@ -1686,12 +1688,14 @@
         </is>
       </c>
       <c r="G23" s="26" t="n"/>
-      <c r="H23" s="29" t="n"/>
+      <c r="H23" s="29" t="n">
+        <v>46309</v>
+      </c>
       <c r="I23" s="26" t="n"/>
       <c r="J23" s="29" t="n"/>
       <c r="K23" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L23" s="27" t="n"/>
@@ -1724,15 +1728,25 @@
         </is>
       </c>
       <c r="G24" s="26" t="n"/>
-      <c r="H24" s="29" t="n"/>
-      <c r="I24" s="26" t="n"/>
+      <c r="H24" s="29" t="n">
+        <v>46310</v>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J24" s="29" t="n"/>
       <c r="K24" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="L24" s="27" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L24" s="27" t="inlineStr">
+        <is>
+          <t>参照题解写单调栈，主循环一次写对；末尾多写了 while(st.empty())——漏了 !，空栈 top/pop 是 UB，而且本来就多余（res 已初始化为 0）。教训：加循环前先问「条件何时为真、循环体在那种情况下安全吗」。</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" s="24">
       <c r="A25" s="26" t="n">
@@ -3140,12 +3154,14 @@
         </is>
       </c>
       <c r="G60" s="26" t="n"/>
-      <c r="H60" s="29" t="n"/>
+      <c r="H60" s="29" t="n">
+        <v>46309</v>
+      </c>
       <c r="I60" s="26" t="n"/>
       <c r="J60" s="29" t="n"/>
       <c r="K60" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L60" s="27" t="n"/>

--- a/力扣学习计划/刷题进度表.xlsx
+++ b/力扣学习计划/刷题进度表.xlsx
@@ -1776,12 +1776,14 @@
         </is>
       </c>
       <c r="G25" s="26" t="n"/>
-      <c r="H25" s="29" t="n"/>
+      <c r="H25" s="29" t="n">
+        <v>46311</v>
+      </c>
       <c r="I25" s="26" t="n"/>
       <c r="J25" s="29" t="n"/>
       <c r="K25" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L25" s="27" t="n"/>
@@ -1814,15 +1816,21 @@
         </is>
       </c>
       <c r="G26" s="26" t="n"/>
-      <c r="H26" s="29" t="n"/>
+      <c r="H26" s="29" t="n">
+        <v>46312</v>
+      </c>
       <c r="I26" s="26" t="n"/>
       <c r="J26" s="29" t="n"/>
       <c r="K26" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="L26" s="27" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L26" s="27" t="inlineStr">
+        <is>
+          <t>骨架（哨兵+弹出结算）写对，但边界取错对象：把被弹的元素当左边界、第一个被弹的当下边界。正确：右边界 = i，左边界 = pop 后的新栈顶。</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="24">
       <c r="A27" s="26" t="n">

--- a/力扣学习计划/刷题进度表.xlsx
+++ b/力扣学习计划/刷题进度表.xlsx
@@ -1860,15 +1860,21 @@
         </is>
       </c>
       <c r="G27" s="26" t="n"/>
-      <c r="H27" s="29" t="n"/>
+      <c r="H27" s="29" t="n">
+        <v>46313</v>
+      </c>
       <c r="I27" s="26" t="n"/>
       <c r="J27" s="29" t="n"/>
       <c r="K27" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="L27" s="27" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L27" s="27" t="inlineStr">
+        <is>
+          <t>凭印象一次写对闭区间模板；后续补上 (int)nums.size() 与 left+(right-left)/2 两处防坑写法。</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" s="24">
       <c r="A28" s="26" t="n">
@@ -1936,15 +1942,21 @@
         </is>
       </c>
       <c r="G29" s="26" t="n"/>
-      <c r="H29" s="29" t="n"/>
+      <c r="H29" s="29" t="n">
+        <v>46313</v>
+      </c>
       <c r="I29" s="26" t="n"/>
       <c r="J29" s="29" t="n"/>
       <c r="K29" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="L29" s="27" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L29" s="27" t="inlineStr">
+        <is>
+          <t>二分答案框架对，但判断函数两处错：ceil(p/mid) 实为整数除法、time&lt;=h 写成 &lt;h。两 bug 方向相反互相掩护，8/16 失败。向上取整要用 (p+mid-1)/mid。</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="14.25" customHeight="1" s="24">
       <c r="A30" s="26" t="n">

--- a/力扣学习计划/刷题进度表.xlsx
+++ b/力扣学习计划/刷题进度表.xlsx
@@ -1904,12 +1904,14 @@
         </is>
       </c>
       <c r="G28" s="26" t="n"/>
-      <c r="H28" s="29" t="n"/>
+      <c r="H28" s="29" t="n">
+        <v>46316</v>
+      </c>
       <c r="I28" s="26" t="n"/>
       <c r="J28" s="29" t="n"/>
       <c r="K28" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L28" s="27" t="n"/>
@@ -1986,15 +1988,21 @@
         </is>
       </c>
       <c r="G30" s="26" t="n"/>
-      <c r="H30" s="29" t="n"/>
+      <c r="H30" s="29" t="n">
+        <v>46316</v>
+      </c>
       <c r="I30" s="26" t="n"/>
       <c r="J30" s="29" t="n"/>
       <c r="K30" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="L30" s="27" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L30" s="27" t="inlineStr">
+        <is>
+          <t>自写的「两抓手（left 在第一段、right 在第二段）+ 特判未旋转」一次通过 18/18；但这套写法依赖元素互不相同——154 含重复时第一行特判就失效，需换成「三支 + 相等时 hi--」。</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="24">
       <c r="A31" s="26" t="n">
@@ -2024,15 +2032,21 @@
         </is>
       </c>
       <c r="G31" s="26" t="n"/>
-      <c r="H31" s="29" t="n"/>
+      <c r="H31" s="29" t="n">
+        <v>46320</v>
+      </c>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="29" t="n"/>
       <c r="K31" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="L31" s="27" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L31" s="27" t="inlineStr">
+        <is>
+          <t>四分支二分。核心：每轮只判断「完好的那一半」，断崖侧靠排除法；nums[lo] &lt;= nums[mid] 的等号在窗口缩到 2 元素 [大,小] 时决定成败，漏掉就把答案推丢。</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" s="24">
       <c r="A32" s="26" t="n">
@@ -4724,15 +4738,21 @@
         </is>
       </c>
       <c r="G100" s="26" t="n"/>
-      <c r="H100" s="29" t="n"/>
+      <c r="H100" s="29" t="n">
+        <v>46319</v>
+      </c>
       <c r="I100" s="26" t="n"/>
       <c r="J100" s="29" t="n"/>
       <c r="K100" s="30" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="L100" s="27" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L100" s="27" t="inlineStr">
+        <is>
+          <t>完全背包一维滚动：容量正序 = 可重复取（倒序退化成 01 背包，[1,2,5] 凑 11 会答 -1）；INF 取 amount+1 而不是 INT_MAX，避免 dp[src]+1 溢出。</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="14.25" customHeight="1" s="24">
       <c r="A101" s="26" t="n">
